--- a/template-copy.xlsx
+++ b/template-copy.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="文案表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="categories" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -743,6 +744,949 @@
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效品类" error="请从下拉列表中选择品类" type="list">
+      <formula1>categories!$A$1:$A$132</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A132"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BADGE_HOLDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BAG_ACCESSORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BANNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BATH_TOY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BEANIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BELT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BLANKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BUTTON_PIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAKE_TOPPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CANDLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CARDIOLOGY_DEVICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CARRIER</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CHAIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CHRISTMAS_TREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CLIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>COASTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>COSMETIC_BAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>COSTUME_ACCESSORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CRAFT_KIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CUSHION</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DECORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DESK_PAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DIAPER_BAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DISPLAY_ALBUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DOORMAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DOLLHOUSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EARRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FAIRY_LIGHTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FASHION_BELT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FASHION_HANDBAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FLASK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FLOWER_POT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FRAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GARLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GIFT_BAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GLASSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GLOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GREETING_CARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HAIR_BARRETTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HAIR_CLIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HALLOWEEN_COSTUME_ACCESSORIES_SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HANGING_ORNAMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>HOLSTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HONEY_BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>INFLATABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>INSECT_REPELLENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>JEWELRY_BOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>KEYCHAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>KITCHEN_TOOLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>LANTERN</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LANYARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LAPTOP_SLEEVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LUGGAGE_TAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MAGNET</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MAKEUP_BAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MASK</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MEDAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MIRROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NECKLACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>NOTEBOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ORNAMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PACKING_CUBES</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PAINTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PARTY_SUPPLIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PET_TOYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PHONE_CASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PILLOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PLANT_STAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PLASTIC_BAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PLAYSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>POUCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PUPPET</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PUSHPIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>RIBBON</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>RING</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ROPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SCARF</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SCHOOL_SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SCREEN_PROTECTOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SEAT_CUSHION</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SEWING_KIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SHIRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SHOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SHOWER_CURTAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SIGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SILICONE_MAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SOCKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SOFA_COVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STICKER_DECAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STORAGE_BAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STRETCHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STRING_LIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STUDY_DESK</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SUNCATCHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TABLECOVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TABLECLOTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TAPESTRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TEA_TOWEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>THERMOMETER</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>THROW_PILLOW_COVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TOTE_BAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TOY_KITCHEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TRAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TUMBLERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>UMBRELLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>VALENTINES</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>VASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>WALL_ART</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>WALL_DECAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>WALL_MIRROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WATER_BOTTLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>WIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>WINDOW_FILM</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>WRAPPING_PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TEMPLATE_STENCIL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>